--- a/tests/granulometria1.xlsx
+++ b/tests/granulometria1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t xml:space="preserve">DATOS DE Granulometría</t>
   </si>
@@ -31,31 +31,100 @@
     <t xml:space="preserve">Rep</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso Material Seco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso de lata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperatura de Secado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiempo de Secado</t>
+    <t xml:space="preserve">Peso Material Seco (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso de lata (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperatura de Secado (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo de Secado (h)</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de secado</t>
   </si>
   <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97</t>
+    <t xml:space="preserve">152.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.75</t>
   </si>
 </sst>
 </file>
@@ -66,7 +135,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,6 +160,13 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -145,7 +221,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -162,11 +238,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -190,37 +274,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -293,7 +377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -348,128 +432,427 @@
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>209</v>
-      </c>
-      <c r="G3" s="5" t="n">
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="E4" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46068</v>
+      <c r="B19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>46070</v>
       </c>
     </row>
   </sheetData>

--- a/tests/granulometria1.xlsx
+++ b/tests/granulometria1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">DATOS DE Granulometría</t>
   </si>
@@ -46,16 +46,124 @@
     <t xml:space="preserve">Fecha de secado</t>
   </si>
   <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97</t>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T0125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">502.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">525.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">490.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">505.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">505.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">538.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">505.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">498.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.5</t>
   </si>
 </sst>
 </file>
@@ -167,7 +275,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -190,37 +298,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -293,7 +401,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -348,128 +456,1582 @@
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>226</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>209</v>
+        <v>24</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>46068</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
       <c r="E5" s="1" t="n">
-        <v>233</v>
+        <v>105</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>227</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>46068</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>225</v>
+        <v>24</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>46068</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="I12" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46068</v>
+      <c r="E14" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="P14" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="P16" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="P18" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P20" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="P26" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P27" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="P28" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="P29" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="P32" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
